--- a/譲渡リース不足書類.xlsx
+++ b/譲渡リース不足書類.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,87 @@
       </c>
       <c r="G6" s="3" t="n"/>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>福岡達也</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>譲渡リース</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>任意保険</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>未提出</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>岡部光</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>譲渡リース</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>任意保険</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>未提出</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>谷口樹生</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>譲渡リース</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>任意保険</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>未提出</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="F4:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
